--- a/ZonasEscolares/excels/PIURA-MORROPON-CHULUCANAS.xlsx
+++ b/ZonasEscolares/excels/PIURA-MORROPON-CHULUCANAS.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/PIURA-MORROPON-CHULUCANAS.xlsx
+++ b/ZonasEscolares/excels/PIURA-MORROPON-CHULUCANAS.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>305</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-5.093189</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-80.168239</v>
-      </c>
-      <c r="I2" t="n">
-        <v>234</v>
-      </c>
-      <c r="J2" t="n">
-        <v>10</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-5.093189</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-80.168239</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>306 DIVINO MAESTRO</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-5.0984</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-80.1596</v>
-      </c>
-      <c r="I3" t="n">
-        <v>271</v>
-      </c>
-      <c r="J3" t="n">
-        <v>13</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-5.0984</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-80.1596</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>855 JESUS EL BUEN PASTOR</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-5.105797</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-80.170219</v>
-      </c>
-      <c r="I4" t="n">
-        <v>130</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-5.105797</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-80.170219</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>858 ANGEL DE MI GUARDA</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-5.1057</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-80.1705</v>
-      </c>
-      <c r="I5" t="n">
-        <v>199</v>
-      </c>
-      <c r="J5" t="n">
-        <v>9</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-5.1057</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-80.1705</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>SAN RAMON</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-5.088901</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-80.15893800000001</v>
-      </c>
-      <c r="I6" t="n">
-        <v>891</v>
-      </c>
-      <c r="J6" t="n">
-        <v>50</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-5.088901</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-80.158938</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>14611 ROSA DE SANTA MARIA</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-5.09673</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-80.159752</v>
-      </c>
-      <c r="I7" t="n">
-        <v>301</v>
-      </c>
-      <c r="J7" t="n">
-        <v>19</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-5.09673</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-80.159752</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>14615 LA INMACULADA</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-5.097977</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-80.160577</v>
-      </c>
-      <c r="I8" t="n">
-        <v>576</v>
-      </c>
-      <c r="J8" t="n">
-        <v>26</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-5.097977</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-80.160577</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>576</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>14616 SABINA CUEVA CASTILLO</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-5.096575</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-80.16009699999999</v>
-      </c>
-      <c r="I9" t="n">
-        <v>621</v>
-      </c>
-      <c r="J9" t="n">
-        <v>26</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-5.096575</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-80.160097</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>14617 JOSE IGNACIO TAVARA PASAPERA</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-5.092754</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-80.16820199999999</v>
-      </c>
-      <c r="I10" t="n">
-        <v>652</v>
-      </c>
-      <c r="J10" t="n">
-        <v>28</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-5.092754</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-80.168202</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>14619</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-5.05901</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-80.13643999999999</v>
-      </c>
-      <c r="I11" t="n">
-        <v>307</v>
-      </c>
-      <c r="J11" t="n">
-        <v>17</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-5.05901</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-80.13644</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>14624 MARIA ALBINA BACA LEON</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-5.0943</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-80.1999</v>
-      </c>
-      <c r="I12" t="n">
-        <v>464</v>
-      </c>
-      <c r="J12" t="n">
-        <v>21</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-5.0943</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-80.1999</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>464</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>JESUS DIVINO MAESTRO</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-5.169228</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-80.143388</v>
-      </c>
-      <c r="I13" t="n">
-        <v>233</v>
-      </c>
-      <c r="J13" t="n">
-        <v>17</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-5.169228</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-80.143388</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>14891</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-5.0825</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-80.0778</v>
-      </c>
-      <c r="I14" t="n">
-        <v>254</v>
-      </c>
-      <c r="J14" t="n">
-        <v>19</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-5.0825</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-80.0778</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>15109</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-4.982606</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-80.165284</v>
-      </c>
-      <c r="I15" t="n">
-        <v>412</v>
-      </c>
-      <c r="J15" t="n">
-        <v>13</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-4.982606</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-80.165284</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>15298</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-5.0061</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-80.1563</v>
-      </c>
-      <c r="I16" t="n">
-        <v>421</v>
-      </c>
-      <c r="J16" t="n">
-        <v>20</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-5.0061</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-80.1563</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>15362</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-5.0892</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-80.2381</v>
-      </c>
-      <c r="I17" t="n">
-        <v>379</v>
-      </c>
-      <c r="J17" t="n">
-        <v>24</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-5.0892</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-80.2381</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>15423</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-5.018338</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-80.14770300000001</v>
-      </c>
-      <c r="I18" t="n">
-        <v>231</v>
-      </c>
-      <c r="J18" t="n">
-        <v>18</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-5.018338</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-80.147703</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>VICUS</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-5.16395</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-80.14063</v>
-      </c>
-      <c r="I19" t="n">
-        <v>484</v>
-      </c>
-      <c r="J19" t="n">
-        <v>30</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-5.16395</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-80.14063</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>484</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>MARIA AUXILIADORA</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-5.10377</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-80.16981</v>
-      </c>
-      <c r="I20" t="n">
-        <v>632</v>
-      </c>
-      <c r="J20" t="n">
-        <v>40</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-5.10377</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-80.16981</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>INIF 40 ISOLINA BACA HAZ</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-5.098113</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-80.15844199999999</v>
-      </c>
-      <c r="I21" t="n">
-        <v>766</v>
-      </c>
-      <c r="J21" t="n">
-        <v>39</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-5.098113</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-80.158442</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>766</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>JOSE PINTADO BERRU</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-5.06606</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-80.14093</v>
-      </c>
-      <c r="I22" t="n">
-        <v>257</v>
-      </c>
-      <c r="J22" t="n">
-        <v>22</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-5.06606</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-80.14093</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>JOSE GALVEZ EGUSQUIZA</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-5.11174</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-80.06723</v>
-      </c>
-      <c r="I23" t="n">
-        <v>341</v>
-      </c>
-      <c r="J23" t="n">
-        <v>28</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-5.11174</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-80.06723</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>DOS DE MAYO</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-5.00894</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-80.22778</v>
-      </c>
-      <c r="I24" t="n">
-        <v>548</v>
-      </c>
-      <c r="J24" t="n">
-        <v>35</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-5.00894</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-80.22778</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>MIGUEL GRAU</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-5.095547</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-80.19912600000001</v>
-      </c>
-      <c r="I25" t="n">
-        <v>357</v>
-      </c>
-      <c r="J25" t="n">
-        <v>20</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-5.095547</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-80.199126</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>IGNACIO ESCUDERO</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-5.1027</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-80.1605</v>
-      </c>
-      <c r="I26" t="n">
-        <v>294</v>
-      </c>
-      <c r="J26" t="n">
-        <v>25</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-5.1027</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-80.1605</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>MARIA REINA</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-5.09734</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-80.16452</v>
-      </c>
-      <c r="I27" t="n">
-        <v>409</v>
-      </c>
-      <c r="J27" t="n">
-        <v>24</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-5.09734</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-80.16452</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-5.09535</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-80.16486</v>
-      </c>
-      <c r="I28" t="n">
-        <v>230</v>
-      </c>
-      <c r="J28" t="n">
-        <v>13</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-5.09535</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-80.16486</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>20037 SANTISIMA CRUZ</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-5.094948</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-80.16741500000001</v>
-      </c>
-      <c r="I29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J29" t="n">
-        <v>46</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-5.094948</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-80.167415</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>SAN FERNANDO</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-5.04476</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-79.79813799999999</v>
-      </c>
-      <c r="I30" t="n">
-        <v>308</v>
-      </c>
-      <c r="J30" t="n">
-        <v>30</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-5.04476</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-79.798138</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>14643 SANTA ROSA DE LIMA</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-5.215459</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-80.09299799999999</v>
-      </c>
-      <c r="I31" t="n">
-        <v>767</v>
-      </c>
-      <c r="J31" t="n">
-        <v>34</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-5.215459</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-80.092998</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>767</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>ASIS</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-5.10007</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-80.16998</v>
-      </c>
-      <c r="I32" t="n">
-        <v>884</v>
-      </c>
-      <c r="J32" t="n">
-        <v>31</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-5.10007</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-80.16998</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>884</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>JOHANNES GUTEMBERG</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-5.09777</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-80.16808</v>
-      </c>
-      <c r="I33" t="n">
-        <v>437</v>
-      </c>
-      <c r="J33" t="n">
-        <v>14</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-5.09777</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-80.16808</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>437</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>SAN GABRIEL</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-5.0982</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-80.16202</v>
-      </c>
-      <c r="I34" t="n">
-        <v>259</v>
-      </c>
-      <c r="J34" t="n">
-        <v>20</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-5.0982</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-80.16202</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>1582</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-5.09408</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-80.19920999999999</v>
-      </c>
-      <c r="I35" t="n">
-        <v>75</v>
-      </c>
-      <c r="J35" t="n">
-        <v>3</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-5.09408</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-80.19921</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>MATER DEI SCHOOL</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-5.08725</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-80.15841</v>
-      </c>
-      <c r="I36" t="n">
-        <v>128</v>
-      </c>
-      <c r="J36" t="n">
-        <v>9</v>
-      </c>
-      <c r="K36" t="n">
-        <v>1</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-5.08725</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-80.15841</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/PIURA-MORROPON-CHULUCANAS.xlsx
+++ b/ZonasEscolares/excels/PIURA-MORROPON-CHULUCANAS.xlsx
@@ -625,37 +625,37 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>429544</t>
+          <t>429935</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>855 JESUS EL BUEN PASTOR</t>
+          <t>15109</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-5.105797</t>
+          <t>-4.982606</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-80.170219</t>
+          <t>-80.165284</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>412</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -687,37 +687,37 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>429577</t>
+          <t>430458</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>858 ANGEL DE MI GUARDA</t>
+          <t>NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-5.1057</t>
+          <t>-5.09535</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-80.1705</t>
+          <t>-80.16486</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>230</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>429582</t>
+          <t>628464</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SAN RAMON</t>
+          <t>JOHANNES GUTEMBERG</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-5.088901</t>
+          <t>-5.09777</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-80.158938</t>
+          <t>-80.16808</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>437</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>429600</t>
+          <t>429681</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>14611 ROSA DE SANTA MARIA</t>
+          <t>14619</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-5.09673</t>
+          <t>-5.05901</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-80.159752</t>
+          <t>-80.13644</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>307</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>429643</t>
+          <t>429817</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>14615 LA INMACULADA</t>
+          <t>JESUS DIVINO MAESTRO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-5.097977</t>
+          <t>-5.169228</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-80.160577</t>
+          <t>-80.143388</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>233</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>429657</t>
+          <t>430104</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>14616 SABINA CUEVA CASTILLO</t>
+          <t>15423</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-5.096575</t>
+          <t>-5.018338</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-80.160097</t>
+          <t>-80.147703</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>231</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>429662</t>
+          <t>429600</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>14617 JOSE IGNACIO TAVARA PASAPERA</t>
+          <t>14611 ROSA DE SANTA MARIA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-5.092754</t>
+          <t>-5.09673</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-80.168202</t>
+          <t>-80.159752</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>301</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>429681</t>
+          <t>429855</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>14619</t>
+          <t>14891</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-5.05901</t>
+          <t>-5.0825</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-80.13644</t>
+          <t>-80.0778</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>254</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>429723</t>
+          <t>430019</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>14624 MARIA ALBINA BACA LEON</t>
+          <t>15298</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-5.0943</t>
+          <t>-5.0061</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-80.1999</t>
+          <t>-80.1563</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>421</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>429817</t>
+          <t>430364</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JESUS DIVINO MAESTRO</t>
+          <t>MIGUEL GRAU</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-5.169228</t>
+          <t>-5.095547</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-80.143388</t>
+          <t>-80.199126</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>357</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>429855</t>
+          <t>682427</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>14891</t>
+          <t>SAN GABRIEL</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-5.0825</t>
+          <t>-5.0982</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-80.0778</t>
+          <t>-80.16202</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>259</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>429935</t>
+          <t>429723</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>15109</t>
+          <t>14624 MARIA ALBINA BACA LEON</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-4.982606</t>
+          <t>-5.0943</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-80.165284</t>
+          <t>-80.1999</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>464</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>430019</t>
+          <t>430321</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>15298</t>
+          <t>JOSE PINTADO BERRU</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-5.0061</t>
+          <t>-5.06606</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-80.1563</t>
+          <t>-80.14093</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>257</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>430104</t>
+          <t>430439</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>15423</t>
+          <t>MARIA REINA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-5.018338</t>
+          <t>-5.09734</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-80.147703</t>
+          <t>-80.16452</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>409</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,37 +1555,37 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>430255</t>
+          <t>430383</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>VICUS</t>
+          <t>IGNACIO ESCUDERO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-5.16395</t>
+          <t>-5.1027</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-80.14063</t>
+          <t>-80.1605</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>294</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>430284</t>
+          <t>429643</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MARIA AUXILIADORA</t>
+          <t>14615 LA INMACULADA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-5.10377</t>
+          <t>-5.097977</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-80.16981</t>
+          <t>-80.160577</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>576</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>430302</t>
+          <t>429657</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>INIF 40 ISOLINA BACA HAZ</t>
+          <t>14616 SABINA CUEVA CASTILLO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-5.098113</t>
+          <t>-5.096575</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-80.158442</t>
+          <t>-80.160097</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>621</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>430321</t>
+          <t>429662</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>JOSE PINTADO BERRU</t>
+          <t>14617 JOSE IGNACIO TAVARA PASAPERA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-5.06606</t>
+          <t>-5.092754</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-80.14093</t>
+          <t>-80.168202</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>652</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1865,42 +1865,42 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>430340</t>
+          <t>429544</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>DOS DE MAYO</t>
+          <t>855 JESUS EL BUEN PASTOR</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-5.00894</t>
+          <t>-5.105797</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-80.22778</t>
+          <t>-80.170219</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>130</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>430364</t>
+          <t>821230</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MIGUEL GRAU</t>
+          <t>1582</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-5.095547</t>
+          <t>-5.09408</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-80.199126</t>
+          <t>-80.19921</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,37 +1989,37 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>430383</t>
+          <t>430255</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>IGNACIO ESCUDERO</t>
+          <t>VICUS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-5.1027</t>
+          <t>-5.16395</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-80.1605</t>
+          <t>-80.14063</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>484</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>430439</t>
+          <t>431306</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MARIA REINA</t>
+          <t>SAN FERNANDO</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-5.09734</t>
+          <t>-5.04476</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-80.16452</t>
+          <t>-79.798138</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>308</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>430458</t>
+          <t>621392</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE FATIMA</t>
+          <t>ASIS</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-5.09535</t>
+          <t>-5.10007</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-80.16486</t>
+          <t>-80.16998</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>884</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>430477</t>
+          <t>431486</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>20037 SANTISIMA CRUZ</t>
+          <t>14643 SANTA ROSA DE LIMA</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-5.094948</t>
+          <t>-5.215459</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-80.167415</t>
+          <t>-80.092998</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>767</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>431306</t>
+          <t>430340</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>SAN FERNANDO</t>
+          <t>DOS DE MAYO</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-5.04476</t>
+          <t>-5.00894</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-79.798138</t>
+          <t>-80.22778</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>548</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>431486</t>
+          <t>430302</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>14643 SANTA ROSA DE LIMA</t>
+          <t>INIF 40 ISOLINA BACA HAZ</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-5.215459</t>
+          <t>-5.098113</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-80.092998</t>
+          <t>-80.158442</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>766</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>621392</t>
+          <t>430284</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ASIS</t>
+          <t>MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-5.10007</t>
+          <t>-5.10377</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-80.16998</t>
+          <t>-80.16981</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>632</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>628464</t>
+          <t>430477</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>JOHANNES GUTEMBERG</t>
+          <t>20037 SANTISIMA CRUZ</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-5.09777</t>
+          <t>-5.094948</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-80.16808</t>
+          <t>-80.167415</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>682427</t>
+          <t>429582</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>SAN GABRIEL</t>
+          <t>SAN RAMON</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-5.0982</t>
+          <t>-5.088901</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-80.16202</t>
+          <t>-80.158938</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>891</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2547,37 +2547,37 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>821230</t>
+          <t>429577</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1582</t>
+          <t>858 ANGEL DE MI GUARDA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-5.09408</t>
+          <t>-5.1057</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-80.19921</t>
+          <t>-80.1705</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>199</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">

--- a/ZonasEscolares/excels/PIURA-MORROPON-CHULUCANAS.xlsx
+++ b/ZonasEscolares/excels/PIURA-MORROPON-CHULUCANAS.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>429346</t>
+          <t>864620</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>MATER DEI SCHOOL</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-5.093189</t>
+          <t>128</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-80.168239</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>-5.08725</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-80.15841</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>429351</t>
+          <t>821230</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>306 DIVINO MAESTRO</t>
+          <t>1582</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-5.0984</t>
+          <t>75</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-80.1596</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>-5.09408</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-80.19921</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>429935</t>
+          <t>682427</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>15109</t>
+          <t>SAN GABRIEL</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-4.982606</t>
+          <t>259</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-80.165284</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>-5.0982</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-80.16202</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>430458</t>
+          <t>628464</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>NUESTRA SEÑORA DE FATIMA</t>
+          <t>JOHANNES GUTEMBERG</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-5.09535</t>
+          <t>437</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-80.16486</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>-5.09777</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-80.16808</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>628464</t>
+          <t>621392</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>JOHANNES GUTEMBERG</t>
+          <t>ASIS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-5.09777</t>
+          <t>884</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-80.16808</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>-5.10007</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-80.16998</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>429681</t>
+          <t>431486</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>14619</t>
+          <t>14643 SANTA ROSA DE LIMA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-5.05901</t>
+          <t>767</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-80.13644</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>-5.215459</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-80.092998</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>429817</t>
+          <t>431306</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JESUS DIVINO MAESTRO</t>
+          <t>SAN FERNANDO</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-5.169228</t>
+          <t>308</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-80.143388</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>-5.04476</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-79.798138</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>430104</t>
+          <t>430477</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>15423</t>
+          <t>20037 SANTISIMA CRUZ</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-5.018338</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-80.147703</t>
+          <t>46</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>231</t>
+          <t>-5.094948</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-80.167415</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>429600</t>
+          <t>430458</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>14611 ROSA DE SANTA MARIA</t>
+          <t>NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-5.09673</t>
+          <t>230</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-80.159752</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>-5.09535</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-80.16486</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>429855</t>
+          <t>430439</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>14891</t>
+          <t>MARIA REINA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-5.0825</t>
+          <t>409</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-80.0778</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>-5.09734</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-80.16452</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>430019</t>
+          <t>430383</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>15298</t>
+          <t>IGNACIO ESCUDERO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-5.0061</t>
+          <t>294</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-80.1563</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>-5.1027</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-80.1605</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1193,22 +1193,22 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>-5.095547</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>-80.199126</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>357</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>682427</t>
+          <t>430340</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SAN GABRIEL</t>
+          <t>DOS DE MAYO</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-5.0982</t>
+          <t>548</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-80.16202</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>-5.00894</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-80.22778</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>429723</t>
+          <t>430335</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>14624 MARIA ALBINA BACA LEON</t>
+          <t>JOSE GALVEZ EGUSQUIZA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-5.0943</t>
+          <t>341</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-80.1999</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>-5.11174</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-80.06723</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1379,22 +1379,22 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>-5.06606</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>-80.14093</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>430062</t>
+          <t>430302</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>15362</t>
+          <t>INIF 40 ISOLINA BACA HAZ</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-5.0892</t>
+          <t>766</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-80.2381</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>-5.098113</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-80.158442</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>430439</t>
+          <t>430284</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>MARIA REINA</t>
+          <t>MARIA AUXILIADORA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-5.09734</t>
+          <t>632</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-80.16452</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>-5.10377</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-80.16981</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,37 +1555,37 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>430383</t>
+          <t>430255</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>IGNACIO ESCUDERO</t>
+          <t>VICUS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-5.1027</t>
+          <t>484</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-80.1605</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>-5.16395</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-80.14063</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>429643</t>
+          <t>430104</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>14615 LA INMACULADA</t>
+          <t>15423</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-5.097977</t>
+          <t>231</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-80.160577</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>-5.018338</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-80.147703</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>429657</t>
+          <t>430062</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>14616 SABINA CUEVA CASTILLO</t>
+          <t>15362</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-5.096575</t>
+          <t>379</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-80.160097</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>-5.0892</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-80.2381</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>429662</t>
+          <t>430019</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>14617 JOSE IGNACIO TAVARA PASAPERA</t>
+          <t>15298</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-5.092754</t>
+          <t>421</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-80.168202</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>-5.0061</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-80.1563</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>430335</t>
+          <t>429935</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>JOSE GALVEZ EGUSQUIZA</t>
+          <t>15109</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-5.11174</t>
+          <t>412</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-80.06723</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>-4.982606</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-80.165284</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,37 +1865,37 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>429544</t>
+          <t>429855</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>855 JESUS EL BUEN PASTOR</t>
+          <t>14891</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-5.105797</t>
+          <t>254</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-80.170219</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>-5.0825</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-80.0778</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>821230</t>
+          <t>429817</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1582</t>
+          <t>JESUS DIVINO MAESTRO</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-5.09408</t>
+          <t>233</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-80.19921</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>-5.169228</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-80.143388</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,37 +1989,37 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>430255</t>
+          <t>429723</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>VICUS</t>
+          <t>14624 MARIA ALBINA BACA LEON</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-5.16395</t>
+          <t>464</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-80.14063</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>-5.0943</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-80.1999</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>431306</t>
+          <t>429681</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SAN FERNANDO</t>
+          <t>14619</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-5.04476</t>
+          <t>307</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-79.798138</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>-5.05901</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>-80.13644</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>621392</t>
+          <t>429662</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>ASIS</t>
+          <t>14617 JOSE IGNACIO TAVARA PASAPERA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-5.10007</t>
+          <t>652</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-80.16998</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>-5.092754</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-80.168202</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>431486</t>
+          <t>429657</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>14643 SANTA ROSA DE LIMA</t>
+          <t>14616 SABINA CUEVA CASTILLO</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-5.215459</t>
+          <t>621</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-80.092998</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>-5.096575</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-80.160097</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>430340</t>
+          <t>429643</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>DOS DE MAYO</t>
+          <t>14615 LA INMACULADA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-5.00894</t>
+          <t>576</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-80.22778</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>-5.097977</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-80.160577</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>430302</t>
+          <t>429600</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>INIF 40 ISOLINA BACA HAZ</t>
+          <t>14611 ROSA DE SANTA MARIA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-5.098113</t>
+          <t>301</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-80.158442</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>-5.09673</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>-80.159752</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>430284</t>
+          <t>429582</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MARIA AUXILIADORA</t>
+          <t>SAN RAMON</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-5.10377</t>
+          <t>891</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-80.16981</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>-5.088901</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>-80.158938</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2423,37 +2423,37 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>430477</t>
+          <t>429577</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>20037 SANTISIMA CRUZ</t>
+          <t>858 ANGEL DE MI GUARDA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-5.094948</t>
+          <t>199</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-80.167415</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>-5.1057</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-80.1705</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2485,42 +2485,42 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>429582</t>
+          <t>429544</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>SAN RAMON</t>
+          <t>855 JESUS EL BUEN PASTOR</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-5.088901</t>
+          <t>130</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-80.158938</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>-5.105797</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>-80.170219</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2547,37 +2547,37 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>429577</t>
+          <t>429351</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>858 ANGEL DE MI GUARDA</t>
+          <t>306 DIVINO MAESTRO</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-5.1057</t>
+          <t>271</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-80.1705</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>-5.0984</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-80.1596</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2609,37 +2609,37 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>864620</t>
+          <t>429346</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>MATER DEI SCHOOL</t>
+          <t>305</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-5.08725</t>
+          <t>234</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-80.15841</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>-5.093189</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-80.168239</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">

--- a/ZonasEscolares/excels/PIURA-MORROPON-CHULUCANAS.xlsx
+++ b/ZonasEscolares/excels/PIURA-MORROPON-CHULUCANAS.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
